--- a/data/c_Auswertung/Verkehrswende_Auswertung.xlsx
+++ b/data/c_Auswertung/Verkehrswende_Auswertung.xlsx
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>409997.4828138978</v>
+        <v>460491.1996304586</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>45112.4375</v>
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10688.48056416646</v>
+        <v>11085.70701257958</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>44950.86458333334</v>
+        <v>45179.16666666666</v>
       </c>
     </row>
     <row r="4">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>191416.876</v>
+        <v>205536.4363</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>45260.73958333334</v>
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-198373.958</v>
+        <v>-220677.83</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>44977.52083333334</v>
@@ -508,7 +508,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18780.638</v>
+        <v>25971.35</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>44927.125</v>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-18780.638</v>
+        <v>-25971.35</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>44927.375</v>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>160195.31</v>
+        <v>172275.8</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>44946.375</v>
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-160195.31</v>
+        <v>-172275.8</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>44930.375</v>
+        <v>44939.45833333334</v>
       </c>
     </row>
     <row r="10">
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19398.01</v>
+        <v>22430.68</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>44927</v>
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-19398.01</v>
+        <v>-22430.68</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>44927.01041666666</v>
